--- a/examples/example_excel.xlsx
+++ b/examples/example_excel.xlsx
@@ -34,6 +34,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -712,21 +734,45 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2">
-        <f>sales - targets</f>
+      <c r="B18" s="2" cm="1">
+        <f t="array" ref="B18:B21">sales - targets</f>
         <v>2500</v>
       </c>
-      <c r="D18" s="2">
-        <f>sales * 0.95</f>
+      <c r="D18" s="2" cm="1">
+        <f t="array" ref="D18:D21">sales * 0.95</f>
         <v>11875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2">
+        <v>-2700</v>
+      </c>
+      <c r="D19" s="2">
+        <v>7885</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2">
+        <v>3700</v>
+      </c>
+      <c r="D20" s="2">
+        <v>14915</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2">
+        <v>-3800</v>
+      </c>
+      <c r="D21" s="2">
+        <v>8740</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="2">
-        <f>SUM(sales * 1.1) - SUM(sales)</f>
+      <c r="B23" s="2" cm="1">
+        <f t="array" ref="B23">SUM(sales * 1.1) - SUM(sales)</f>
         <v>4570</v>
       </c>
     </row>
